--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -14,24 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
   <si>
     <t/>
   </si>
   <si>
-    <t>no.</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>rating</t>
-  </si>
-  <si>
-    <t>beds</t>
-  </si>
-  <si>
-    <t>mobile no.</t>
+    <t>Srno.</t>
+  </si>
+  <si>
+    <t>Hospital Name</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>No. of Beds</t>
+  </si>
+  <si>
+    <t>Mobile no.</t>
   </si>
   <si>
     <t>1</t>
@@ -46,7 +46,7 @@
     <t>284</t>
   </si>
   <si>
-    <t>08045002241</t>
+    <t>NA</t>
   </si>
   <si>
     <t>2</t>
@@ -61,9 +61,6 @@
     <t>160</t>
   </si>
   <si>
-    <t>08045002243</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>100</t>
   </si>
   <si>
-    <t>08069453912</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -97,7 +91,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>08045002247</t>
   </si>
   <si>
     <t>6</t>
@@ -109,9 +103,6 @@
     <t>20</t>
   </si>
   <si>
-    <t>08047111520</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -142,9 +133,6 @@
     <t>Cloudnine Hospital - Old Airport Road, Old Airport Road</t>
   </si>
   <si>
-    <t>07969202069</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -154,10 +142,31 @@
     <t>415</t>
   </si>
   <si>
-    <t>08037322195</t>
-  </si>
-  <si>
     <t>top cities</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
   </si>
   <si>
     <t>message</t>
@@ -240,6 +249,21 @@
 Testimonials
 FAQs</t>
   </si>
+  <si>
+    <t>08045002241</t>
+  </si>
+  <si>
+    <t>08045002243</t>
+  </si>
+  <si>
+    <t>08047111520</t>
+  </si>
+  <si>
+    <t>03340585891</t>
+  </si>
+  <si>
+    <t>08037322195</t>
+  </si>
 </sst>
 </file>
 
@@ -283,14 +307,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="3.50390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="62.4296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="5.640625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="4.7578125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.9296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.1015625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="62.4296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="6.02734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.9296875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -341,143 +365,313 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>16</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>17</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="E5" t="s" s="0">
         <v>21</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="E6" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="E7" t="s" s="0">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="E8" t="s" s="0">
         <v>33</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>46</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -487,20 +681,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.66796875"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -510,25 +779,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="183.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="183.06640625"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>49</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -14,24 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="62">
   <si>
     <t/>
   </si>
   <si>
-    <t>no.</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>rating</t>
-  </si>
-  <si>
-    <t>beds</t>
-  </si>
-  <si>
-    <t>mobile no.</t>
+    <t>Srno.</t>
+  </si>
+  <si>
+    <t>Hospital Name</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>No. of Beds</t>
+  </si>
+  <si>
+    <t>Mobile no.</t>
   </si>
   <si>
     <t>1</t>
@@ -73,7 +73,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>08069453912</t>
+    <t>NA</t>
   </si>
   <si>
     <t>4</t>
@@ -85,9 +85,6 @@
     <t>42</t>
   </si>
   <si>
-    <t>08047116529</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>50</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>20</t>
   </si>
   <si>
-    <t>08047111520</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -136,6 +127,9 @@
     <t>80</t>
   </si>
   <si>
+    <t>03340585891</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -160,14 +154,34 @@
     <t>top cities</t>
   </si>
   <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
     <t>message</t>
   </si>
   <si>
-    <t>Our ServicesPracto EcosystemProduct CapabilitiesTestimonialsFAQsGroup Insurance
-Your Workplace Health and Wellness Partner
-Over 30cr users benefited by our holistic, customizable and accessible healthcare solutions
-Schedule a Demo
-Organization Size
+    <t>Organization Size
 &lt;500
 501-1000
 1001-5000
@@ -179,150 +193,32 @@
 Enquiring about an existing plan
 A career opportunity
 Schedule a demo
-Our Clients
-Our Services
-Easy Online consultations
-Over 25 specialities guided by best in class doctors for effective care around the clock.
-Online Pharmacy
-COVID-19 essentials and self-test kits provided, along with access to a large inventory for medicines.
-Lab Tests at Home
-Discounts upto 20% on NABL-accredited lab tests and at-home tests in multiple cities.
-Group Health Insurance
-Over 500+ day care procedures covered with a variety of payment options, for employees and family members.
-SOS Ambulance Service
-24/7 round the clock Ambulatory services along with equipped medical staff.
-Mental Wellbeing Solutions
-Specially focused Mental Wellness plans available with regular informative webinars and constant support.
-Covid Care Packages
-Covid-19 specific online consultations, lab tests, medical equipment, SOS assistance, and home care services
-Engagement Activities &amp; Gamification
-Webinars and other knowledge-building sessions, peer-group challenges, and other employee engagement activities
-Why Choose Us?
-For Organizations
-Manage benefits, Improve Communication and Engage Employees
-For Employees
-Better Health, Easy Management and more vitality
-For Leaders
-Culture of Health and Wellness, Peer Interactions
-Practo Ecosystem
-With a rating of 4.5+ we ensure our healthcare solutions are top quality and uniquely personalised to every employee.
-15k+
-Instant consultations per day
-30cr+
-Patients per year
-1.2 lakh+
-Doctor partners
-Demo Video
-Product Capabilities
-ISO 27001 certified
-1
-2
-3
-4
-5
-Testimonials
-Mr. Dilip Chenoy
-Secretary-General
-“We believe in Practo’s commitment to providing high-quality healthcare services to society, and in supporting the country’s working professional community. Practo and FICCI management will be working closely on every step"
-1
-2
-3
-FAQs
-Are the corporate benefits plans applicable to employees’ families?
-Are Practo doctors who conduct online consultations qualified to consult patients online?
-Can I consult a doctor of my choice?
-Know more
-Practo is on a mission to make quality healthcare affordable and accessible for over a billion+ Indians.
-Quick Links
-Our Services
-Practo Ecosystem
-Product Capabilities
-Testimonials
-FAQs</t>
+THANK YOU
+Your demo request has been received. Our team will contact you shortly to follow-up.
+Follow Us
+THANK YOU
+Your demo request has been received. Our team will contact you shortly to follow-up.
+Follow Us</t>
+  </si>
+  <si>
+    <t>THANK YOU
+Your demo request has been received. Our team will contact you shortly to follow-up.
+Follow Us</t>
+  </si>
+  <si>
+    <t>THANK YOU</t>
+  </si>
+  <si>
+    <t>08069453912</t>
+  </si>
+  <si>
+    <t>08047116529</t>
   </si>
   <si>
     <t>08045002247</t>
   </si>
   <si>
-    <t>03340585891</t>
-  </si>
-  <si>
-    <t>Our ServicesPracto EcosystemProduct CapabilitiesTestimonialsFAQsGroup Insurance
-Your Workplace Health and Wellness Partner
-Over 30cr users benefited by our holistic, customizable and accessible healthcare solutions
-Schedule a Demo
-Organization Size
-&lt;500
-501-1000
-1001-5000
-5001-10000
-10001+
-Interested In
-Taking a demo
-Referring someone
-Enquiring about an existing plan
-A career opportunity
-Schedule a demo
-Our Clients
-Our Services
-Easy Online consultations
-Over 25 specialities guided by best in class doctors for effective care around the clock.
-Online Pharmacy
-COVID-19 essentials and self-test kits provided, along with access to a large inventory for medicines.
-Lab Tests at Home
-Discounts upto 20% on NABL-accredited lab tests and at-home tests in multiple cities.
-Group Health Insurance
-Over 500+ day care procedures covered with a variety of payment options, for employees and family members.
-SOS Ambulance Service
-24/7 round the clock Ambulatory services along with equipped medical staff.
-Mental Wellbeing Solutions
-Specially focused Mental Wellness plans available with regular informative webinars and constant support.
-Covid Care Packages
-Covid-19 specific online consultations, lab tests, medical equipment, SOS assistance, and home care services
-Engagement Activities &amp; Gamification
-Webinars and other knowledge-building sessions, peer-group challenges, and other employee engagement activities
-Why Choose Us?
-For Organizations
-Manage benefits, Improve Communication and Engage Employees
-For Employees
-Better Health, Easy Management and more vitality
-For Leaders
-Culture of Health and Wellness, Peer Interactions
-Practo Ecosystem
-With a rating of 4.5+ we ensure our healthcare solutions are top quality and uniquely personalised to every employee.
-15k+
-Instant consultations per day
-30cr+
-Patients per year
-1.2 lakh+
-Doctor partners
-Demo Video
-Product Capabilities
-Access to a large repository of health articles written by medical experts
-1
-2
-3
-4
-5
-Testimonials
-Mr. Dilip Chenoy
-Secretary-General
-“We believe in Practo’s commitment to providing high-quality healthcare services to society, and in supporting the country’s working professional community. Practo and FICCI management will be working closely on every step"
-1
-2
-3
-FAQs
-Are the corporate benefits plans applicable to employees’ families?
-Are Practo doctors who conduct online consultations qualified to consult patients online?
-Can I consult a doctor of my choice?
-Know more
-Practo is on a mission to make quality healthcare affordable and accessible for over a billion+ Indians.
-Quick Links
-Our Services
-Practo Ecosystem
-Product Capabilities
-Testimonials
-FAQs</t>
+    <t>08047111520</t>
   </si>
 </sst>
 </file>
@@ -370,10 +266,10 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="3.50390625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.1015625"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="62.4296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.7578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="6.02734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.140625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="11.9296875"/>
   </cols>
   <sheetData>
@@ -459,109 +355,109 @@
         <v>22</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="C6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>26</v>
-      </c>
       <c r="E6" t="s" s="0">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="E7" t="s" s="0">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="E8" t="s" s="0">
         <v>33</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>37</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s" s="0">
         <v>40</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -612,7 +508,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -629,109 +525,109 @@
         <v>22</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="C16" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C16" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>26</v>
-      </c>
       <c r="E16" t="s" s="0">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="E17" t="s" s="0">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="E18" t="s" s="0">
         <v>33</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s" s="0">
         <v>37</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s" s="0">
         <v>40</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -741,25 +637,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="8.26953125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.66796875"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>27</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -769,35 +735,135 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="183.06640625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="69.75"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>52</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="63">
   <si>
     <t/>
   </si>
@@ -219,6 +219,84 @@
   </si>
   <si>
     <t>08047111520</t>
+  </si>
+  <si>
+    <t>Our ServicesPracto EcosystemProduct CapabilitiesTestimonialsFAQsGroup Insurance
+Your Workplace Health and Wellness Partner
+Over 30cr users benefited by our holistic, customizable and accessible healthcare solutions
+Schedule a Demo
+Organization Size
+&lt;500
+501-1000
+1001-5000
+5001-10000
+10001+
+Interested In
+Taking a demo
+Referring someone
+Enquiring about an existing plan
+A career opportunity
+Schedule a demo
+Our Clients
+Our Services
+Easy Online consultations
+Over 25 specialities guided by best in class doctors for effective care around the clock.
+Online Pharmacy
+COVID-19 essentials and self-test kits provided, along with access to a large inventory for medicines.
+Lab Tests at Home
+Discounts upto 20% on NABL-accredited lab tests and at-home tests in multiple cities.
+Group Health Insurance
+Over 500+ day care procedures covered with a variety of payment options, for employees and family members.
+SOS Ambulance Service
+24/7 round the clock Ambulatory services along with equipped medical staff.
+Mental Wellbeing Solutions
+Specially focused Mental Wellness plans available with regular informative webinars and constant support.
+Covid Care Packages
+Covid-19 specific online consultations, lab tests, medical equipment, SOS assistance, and home care services
+Engagement Activities &amp; Gamification
+Webinars and other knowledge-building sessions, peer-group challenges, and other employee engagement activities
+Why Choose Us?
+For Organizations
+Manage benefits, Improve Communication and Engage Employees
+For Employees
+Better Health, Easy Management and more vitality
+For Leaders
+Culture of Health and Wellness, Peer Interactions
+Practo Ecosystem
+With a rating of 4.5+ we ensure our healthcare solutions are top quality and uniquely personalised to every employee.
+15k+
+Instant consultations per day
+30cr+
+Patients per year
+1.2 lakh+
+Doctor partners
+Demo Video
+Product Capabilities
+All records stored on secure servers
+1
+2
+3
+4
+5
+Testimonials
+Mr. Naveen Tahilyani
+MD &amp; CEO
+"Through this partnership, beyond synergies at both sides, the consumers of Practo can access best-in-class solutions for safeguarding themselves and building a healthier life".
+1
+2
+3
+FAQs
+Are the corporate benefits plans applicable to employees’ families?
+Are Practo doctors who conduct online consultations qualified to consult patients online?
+Can I consult a doctor of my choice?
+Know more
+Practo is on a mission to make quality healthcare affordable and accessible for over a billion+ Indians.
+Quick Links
+Our Services
+Practo Ecosystem
+Product Capabilities
+Testimonials
+FAQs</t>
   </si>
 </sst>
 </file>
@@ -263,7 +341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="5.1015625"/>
@@ -630,6 +708,346 @@
         <v>44</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -637,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="10.66796875"/>
@@ -728,6 +1146,86 @@
         <v>53</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -735,10 +1233,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="69.75"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="141.46484375"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,6 +1364,26 @@
         <v>57</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="59">
   <si>
     <t/>
   </si>
@@ -46,7 +46,7 @@
     <t>284</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>08045002241</t>
   </si>
   <si>
     <t>2</t>
@@ -61,6 +61,9 @@
     <t>160</t>
   </si>
   <si>
+    <t>08045002243</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>100</t>
   </si>
   <si>
+    <t>08069453912</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t>20</t>
   </si>
   <si>
+    <t>08047111520</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -127,12 +136,18 @@
     <t>80</t>
   </si>
   <si>
+    <t>03340585891</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
     <t>Cloudnine Hospital - Old Airport Road, Old Airport Road</t>
   </si>
   <si>
+    <t>07969202069</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -140,6 +155,9 @@
   </si>
   <si>
     <t>415</t>
+  </si>
+  <si>
+    <t>08037322195</t>
   </si>
   <si>
     <t>top cities</t>
@@ -223,16 +241,16 @@
 Doctor partners
 Demo Video
 Product Capabilities
-ISO 27001 certified
+All records stored on secure servers
 1
 2
 3
 4
 5
 Testimonials
-Mr. Dilip Chenoy
-Secretary-General
-“We believe in Practo’s commitment to providing high-quality healthcare services to society, and in supporting the country’s working professional community. Practo and FICCI management will be working closely on every step"
+Mr. Naveen Tahilyani
+MD &amp; CEO
+"Through this partnership, beyond synergies at both sides, the consumers of Practo can access best-in-class solutions for safeguarding themselves and building a healthier life".
 1
 2
 3
@@ -248,21 +266,6 @@
 Product Capabilities
 Testimonials
 FAQs</t>
-  </si>
-  <si>
-    <t>08045002241</t>
-  </si>
-  <si>
-    <t>08045002243</t>
-  </si>
-  <si>
-    <t>08047111520</t>
-  </si>
-  <si>
-    <t>03340585891</t>
-  </si>
-  <si>
-    <t>08037322195</t>
   </si>
 </sst>
 </file>
@@ -307,14 +310,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.1015625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="62.4296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="6.02734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.9296875"/>
+    <col min="1" max="1" width="5.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="62.4296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.02734375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.140625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.9296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -365,313 +368,143 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>13</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -681,95 +514,55 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="10.66796875"/>
+    <col min="1" max="1" width="10.66796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -779,35 +572,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="183.06640625"/>
+    <col min="1" max="1" width="141.46484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -241,7 +241,7 @@
 Doctor partners
 Demo Video
 Product Capabilities
-All records stored on secure servers
+Dedicated dashboard for HRs for easy access and management
 1
 2
 3

--- a/output/PractoData.xlsx
+++ b/output/PractoData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -298,6 +298,84 @@
 Testimonials
 FAQs</t>
   </si>
+  <si>
+    <t>Our ServicesPracto EcosystemProduct CapabilitiesTestimonialsFAQsGroup Insurance
+Your Workplace Health and Wellness Partner
+Over 30cr users benefited by our holistic, customizable and accessible healthcare solutions
+Schedule a Demo
+Organization Size
+&lt;500
+501-1000
+1001-5000
+5001-10000
+10001+
+Interested In
+Taking a demo
+Referring someone
+Enquiring about an existing plan
+A career opportunity
+Schedule a demo
+Our Clients
+Our Services
+Easy Online consultations
+Over 25 specialities guided by best in class doctors for effective care around the clock.
+Online Pharmacy
+COVID-19 essentials and self-test kits provided, along with access to a large inventory for medicines.
+Lab Tests at Home
+Discounts upto 20% on NABL-accredited lab tests and at-home tests in multiple cities.
+Group Health Insurance
+Over 500+ day care procedures covered with a variety of payment options, for employees and family members.
+SOS Ambulance Service
+24/7 round the clock Ambulatory services along with equipped medical staff.
+Mental Wellbeing Solutions
+Specially focused Mental Wellness plans available with regular informative webinars and constant support.
+Covid Care Packages
+Covid-19 specific online consultations, lab tests, medical equipment, SOS assistance, and home care services
+Engagement Activities &amp; Gamification
+Webinars and other knowledge-building sessions, peer-group challenges, and other employee engagement activities
+Why Choose Us?
+For Organizations
+Manage benefits, Improve Communication and Engage Employees
+For Employees
+Better Health, Easy Management and more vitality
+For Leaders
+Culture of Health and Wellness, Peer Interactions
+Practo Ecosystem
+With a rating of 4.5+ we ensure our healthcare solutions are top quality and uniquely personalised to every employee.
+15k+
+Instant consultations per day
+30cr+
+Patients per year
+1.2 lakh+
+Doctor partners
+Demo Video
+Product Capabilities
+Easy-to-use interface
+1
+2
+3
+4
+5
+Testimonials
+Mr. Varun Sheth
+Co-founder &amp; CEO
+"Inspired with the idea of ‘giving that gives back’ the social impact plan is focused on creating a community that believes in building a healthy India. It is our paramount responsibility to look after our donors whose relentless efforts are saving so many lives. We are very delighted to partner with Practo which echoes the same emotion, compassion, and passion towards building a healthy India."
+1
+2
+3
+FAQs
+Are the corporate benefits plans applicable to employees’ families?
+Are Practo doctors who conduct online consultations qualified to consult patients online?
+Can I consult a doctor of my choice?
+Know more
+Practo is on a mission to make quality healthcare affordable and accessible for over a billion+ Indians.
+Quick Links
+Our Services
+Practo Ecosystem
+Product Capabilities
+Testimonials
+FAQs</t>
+  </si>
 </sst>
 </file>
 
@@ -341,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="5.1015625"/>
@@ -1048,6 +1126,176 @@
         <v>44</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1055,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="10.66796875"/>
@@ -1226,6 +1474,46 @@
         <v>53</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1233,10 +1521,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="141.46484375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="255.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1384,6 +1672,16 @@
         <v>62</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
